--- a/data/migration_perspectives/quotes.xlsx
+++ b/data/migration_perspectives/quotes.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="401">
   <si>
     <t>Interview id</t>
   </si>
@@ -1112,12 +1112,141 @@
   <si>
     <t>Working was like this. The children came one after another. I had a daughter. My daughter was one and a half years old. Then I had a son. They came one after another. I raised them like twins. After that, I raised them both, and just as I was saying they were getting out of hand, I was taking them to kindergarten. The hours were long there too. I took them at 8:30. They were there until 4:00. I was available. I thought I'd work... The hours were long. I wanted to work, but as I said, my husband always stood in my way. He didn't want me to.</t>
   </si>
+  <si>
+    <t>ESP_P01</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Jobs usually require Spanish. I even tried, I was on a trial period at such a large real estate firm, but there was that condition that Spanish was necessary, so…</t>
+  </si>
+  <si>
+    <t>ESP_P02</t>
+  </si>
+  <si>
+    <t>I believe that Spain is not inclined to cooperate and that Poland does not care at all, because Poland, for example, as you know, does not mind that we have other nationalities; it is not of concern to them. Your Polish nationality will not be taken away from you; it could only be revoked by the President of Poland if you request it.</t>
+  </si>
+  <si>
+    <t>ESP_P03</t>
+  </si>
+  <si>
+    <t>In Poland, we're really going all out; we don't let newcomers stay, we want to kick them all out. You know, that's pretty harsh, right? I mean, I'm not a politician, so I don't really know, but this immigration thing has become a huge topic, a huge topic; it's the big issue for politicians.</t>
+  </si>
+  <si>
+    <t>ESP_P04</t>
+  </si>
+  <si>
+    <t>I mean I will always be Polish, but I have definitely been influenced by the culture, society, and life here</t>
+  </si>
+  <si>
+    <t>ESP_P05</t>
+  </si>
+  <si>
+    <t>you notice the sheer number of people buying properties here in Spain, especially in this sun-drenched epicenter, and they tend to be somewhat more affluent.</t>
+  </si>
+  <si>
+    <t>ESP_P06</t>
+  </si>
+  <si>
+    <t>In Poland, wealthy individuals often buy apartments in areas of Alicante. I know this because there are direct flights from Warsaw to Alicante, and Warsaw is a capital city where people can earn a lot.</t>
+  </si>
+  <si>
+    <t>ESP_P07</t>
+  </si>
+  <si>
+    <t>Brexit has had an impact on this, because it allowed for such movements. Previously, Poles were going to England, to Ireland, and so on. Those who were in England, if they wanted to return, then they indeed returned.</t>
+  </si>
+  <si>
+    <t>ESP_P08</t>
+  </si>
+  <si>
+    <t>My parents receive pensions. They are independent, and my brother runs his own business.</t>
+  </si>
+  <si>
+    <t>ESP_P09</t>
+  </si>
+  <si>
+    <t>[Polish migrants] starting to earn money here [in Spain], doing well, and realizing that it's not just about coming to work but actually living quite well. They began to attract their families, who then moved here too. This was quite common, especially at the beginning of the 2000s to 2010, on the Costa del Sol, where there were many Polish groups.</t>
+  </si>
+  <si>
+    <t>ESP_P10</t>
+  </si>
+  <si>
+    <t>The Polish community we have here now is somewhat different because, due to the presence of the university and the vibrant life around it, most of the Polish community consists of people with higher education.</t>
+  </si>
+  <si>
+    <t>ESP_P11</t>
+  </si>
+  <si>
+    <t>The main reason, of course, was love, as my partner lives here in Madrid. We also met through my family, who has lived here for many years. After the pandemic, we decided that if we ever faced another six-month winter again, we should live together in the same place.</t>
+  </si>
+  <si>
+    <t>ESP_P12</t>
+  </si>
+  <si>
+    <t>Well, many of these people are working remotely and choosing to live here in Spain. They say things like, 'Look, I can live here, my kids are learning the language, I get sunshine 360 days a year.' Life here is different; it feels more relaxed and calm, far from the tensions of war and political unrest.</t>
+  </si>
+  <si>
+    <t>ESP_P13</t>
+  </si>
+  <si>
+    <t>Apartments here are even cheaper than in Poland. You can buy a house here while in Poland you can only buy an apartment. So, this is definitely a plus... Plus, there's great weather and peace of mind, which is wonderful</t>
+  </si>
+  <si>
+    <t>ESP_P14</t>
+  </si>
+  <si>
+    <t>Just imagine that someday my brothers—one will turn 18 very soon, and the other in two years—will be told, 'Hey, we have to go to Military. Yes, it's about creating an army, right? Ultimately, many people in Poland are very afraid of that. There may also be young people wanting to leave Poland to avoid this recruitment</t>
+  </si>
+  <si>
+    <t>ESP_P15</t>
+  </si>
+  <si>
+    <t>If Poland tries to recruit me to go to the front, I will indeed make it [Spanish nationality] so that the Spanish government does not hand me over to the front in Poland through the Mossos Esquadra,</t>
+  </si>
+  <si>
+    <t>ESP_P16</t>
+  </si>
+  <si>
+    <t>Well, if they were same-sex couples, I can't even begin to describe it, because there [in Poland], neither civil partnerships nor marriages for same-sex individuals are allowed. These individuals often felt very overwhelmed by the political climate.</t>
+  </si>
+  <si>
+    <t>ESP_P17</t>
+  </si>
+  <si>
+    <t>They have the advantage that they have such nice weather here, while in Poland it's nice for two months a year, sometimes three, if luck has it, and then there is such grayness, all those nice places, are closed, covered in snow</t>
+  </si>
+  <si>
+    <t>ESP_P18</t>
+  </si>
+  <si>
+    <t>Many people come and feel that Spaniards are quite open, especially here in the south. They are really welcoming, and it’s easy to make friends. It's true that if you go to the same fruit shop five times, your fruit vendor will already recognize you, and you'll end up joking around with him, but this is only possible if you speak the language.</t>
+  </si>
+  <si>
+    <t>ESP_P19</t>
+  </si>
+  <si>
+    <t>As for apartments, it seems to me that this may be related to occupation and the laws in place here, as owners are somewhat hesitant to rent to unverified individuals, or even to rent without the mediation of companies that handle these matters.</t>
+  </si>
+  <si>
+    <t>ESP_P20</t>
+  </si>
+  <si>
+    <t>The main problem regarding the Polish community that comes to the vicinity of Valencia and Alicante is the language issue, especially if there are children in the family, as these children do not adapt as quickly as parents might always expect. We discussed teenagers, as elementary school children are unlikely to have this issue, but they are at a different stage and probably find it easier in winter.</t>
+  </si>
+  <si>
+    <t>ESP_P21</t>
+  </si>
+  <si>
+    <t>I have the impression, at least for me, that it would be easier for me to find a new job in Poland than in Spain. I have the impression that the job market in Spain is worse, making it more difficult to find a job than in Poland</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1200,8 +1329,13 @@
       <color rgb="FF000000"/>
       <name val="&quot;\0027Times New Roman\0027&quot;"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1238,8 +1372,26 @@
         <bgColor rgb="FFE6B8AF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor rgb="FFD8E4BC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76933C"/>
+        <bgColor rgb="FF76933C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border/>
     <border>
       <left style="thin">
@@ -1495,11 +1647,36 @@
         <color rgb="FF284E3F"/>
       </right>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="123">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1829,6 +2006,45 @@
     </xf>
     <xf borderId="18" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="20" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="20" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="20" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="20" fillId="7" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="20" fillId="9" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="21" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="21" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="21" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="21" fillId="7" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="21" fillId="9" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="21" fillId="8" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="21" fillId="7" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22786,6 +23002,1686 @@
         <v>357</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" s="110" t="s">
+        <v>358</v>
+      </c>
+      <c r="B260" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C260" s="110" t="s">
+        <v>130</v>
+      </c>
+      <c r="D260" s="111" t="s">
+        <v>103</v>
+      </c>
+      <c r="E260" s="110" t="s">
+        <v>36</v>
+      </c>
+      <c r="F260" s="110" t="s">
+        <v>31</v>
+      </c>
+      <c r="G260" s="110" t="s">
+        <v>359</v>
+      </c>
+      <c r="H260" s="112">
+        <v>0.0</v>
+      </c>
+      <c r="I260" s="112">
+        <v>1.0</v>
+      </c>
+      <c r="J260" s="112">
+        <v>0.0</v>
+      </c>
+      <c r="K260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="L260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="M260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="N260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="O260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="P260" s="113">
+        <v>1.0</v>
+      </c>
+      <c r="Q260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="R260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="S260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="T260" s="113">
+        <v>1.0</v>
+      </c>
+      <c r="U260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="V260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="W260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="X260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="Y260" s="113">
+        <v>0.0</v>
+      </c>
+      <c r="Z260" s="114" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="115" t="s">
+        <v>361</v>
+      </c>
+      <c r="B261" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C261" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D261" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E261" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F261" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G261" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H261" s="117">
+        <v>1.0</v>
+      </c>
+      <c r="I261" s="117">
+        <v>0.0</v>
+      </c>
+      <c r="J261" s="117">
+        <v>0.0</v>
+      </c>
+      <c r="K261" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="L261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O261" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="P261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X261" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Y261" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z261" s="119" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="115" t="s">
+        <v>363</v>
+      </c>
+      <c r="B262" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C262" s="115" t="s">
+        <v>102</v>
+      </c>
+      <c r="D262" s="116" t="s">
+        <v>103</v>
+      </c>
+      <c r="E262" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F262" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G262" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H262" s="117">
+        <v>0.0</v>
+      </c>
+      <c r="I262" s="117">
+        <v>1.0</v>
+      </c>
+      <c r="J262" s="117">
+        <v>0.0</v>
+      </c>
+      <c r="K262" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="L262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y262" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z262" s="119" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="115" t="s">
+        <v>365</v>
+      </c>
+      <c r="B263" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C263" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D263" s="116" t="s">
+        <v>103</v>
+      </c>
+      <c r="E263" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F263" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G263" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H263" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="I263" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J263" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O263" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="P263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X263" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Y263" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z263" s="119" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="115" t="s">
+        <v>367</v>
+      </c>
+      <c r="B264" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C264" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D264" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E264" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F264" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G264" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H264" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I264" s="117">
+        <v>1.0</v>
+      </c>
+      <c r="J264" s="117">
+        <v>0.0</v>
+      </c>
+      <c r="K264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M264" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="N264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X264" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y264" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Z264" s="119" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="115" t="s">
+        <v>369</v>
+      </c>
+      <c r="B265" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C265" s="121" t="s">
+        <v>102</v>
+      </c>
+      <c r="D265" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E265" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F265" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G265" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H265" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I265" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J265" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="K265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M265" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="N265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W265" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="X265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y265" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z265" s="119" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="115" t="s">
+        <v>371</v>
+      </c>
+      <c r="B266" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C266" s="121" t="s">
+        <v>130</v>
+      </c>
+      <c r="D266" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E266" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F266" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G266" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H266" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I266" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="J266" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V266" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="W266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X266" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y266" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Z266" s="119" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="115" t="s">
+        <v>373</v>
+      </c>
+      <c r="B267" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C267" s="121" t="s">
+        <v>102</v>
+      </c>
+      <c r="D267" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E267" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F267" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G267" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H267" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I267" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="J267" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N267" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="O267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y267" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z267" s="119" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="115" t="s">
+        <v>375</v>
+      </c>
+      <c r="B268" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C268" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D268" s="116" t="s">
+        <v>103</v>
+      </c>
+      <c r="E268" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F268" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G268" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H268" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I268" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="J268" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N268" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="O268" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="P268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T268" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="U268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y268" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z268" s="119" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="115" t="s">
+        <v>377</v>
+      </c>
+      <c r="B269" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C269" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D269" s="116" t="s">
+        <v>103</v>
+      </c>
+      <c r="E269" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F269" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G269" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H269" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I269" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="J269" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L269" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="M269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T269" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="U269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X269" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y269" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Z269" s="119" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="115" t="s">
+        <v>379</v>
+      </c>
+      <c r="B270" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C270" s="121" t="s">
+        <v>102</v>
+      </c>
+      <c r="D270" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E270" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F270" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G270" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H270" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="I270" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J270" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O270" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="P270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W270" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="X270" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Y270" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z270" s="119" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="115" t="s">
+        <v>381</v>
+      </c>
+      <c r="B271" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C271" s="121" t="s">
+        <v>130</v>
+      </c>
+      <c r="D271" s="118" t="s">
+        <v>103</v>
+      </c>
+      <c r="E271" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F271" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G271" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H271" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I271" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J271" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="K271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L271" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="M271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O271" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="P271" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Q271" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="R271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T271" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="U271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W271" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="X271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y271" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z271" s="119" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="115" t="s">
+        <v>383</v>
+      </c>
+      <c r="B272" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C272" s="121" t="s">
+        <v>102</v>
+      </c>
+      <c r="D272" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E272" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F272" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G272" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H272" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I272" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="J272" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M272" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="N272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q272" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="R272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U272" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="V272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W272" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="X272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y272" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z272" s="119" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="115" t="s">
+        <v>385</v>
+      </c>
+      <c r="B273" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C273" s="121" t="s">
+        <v>102</v>
+      </c>
+      <c r="D273" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E273" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F273" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G273" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H273" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I273" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J273" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="K273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W273" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="X273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y273" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z273" s="119" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="115" t="s">
+        <v>387</v>
+      </c>
+      <c r="B274" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C274" s="121" t="s">
+        <v>102</v>
+      </c>
+      <c r="D274" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E274" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F274" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G274" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H274" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="I274" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J274" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O274" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="P274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V274" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="W274" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="X274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y274" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z274" s="119" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="115" t="s">
+        <v>389</v>
+      </c>
+      <c r="B275" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C275" s="121" t="s">
+        <v>130</v>
+      </c>
+      <c r="D275" s="118" t="s">
+        <v>103</v>
+      </c>
+      <c r="E275" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F275" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G275" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H275" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="I275" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J275" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K275" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="L275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V275" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="W275" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="X275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y275" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z275" s="119" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="115" t="s">
+        <v>391</v>
+      </c>
+      <c r="B276" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C276" s="121" t="s">
+        <v>102</v>
+      </c>
+      <c r="D276" s="118" t="s">
+        <v>103</v>
+      </c>
+      <c r="E276" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F276" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G276" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H276" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I276" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J276" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="K276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q276" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="R276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U276" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="V276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W276" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="X276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y276" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z276" s="119" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="115" t="s">
+        <v>393</v>
+      </c>
+      <c r="B277" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C277" s="121" t="s">
+        <v>130</v>
+      </c>
+      <c r="D277" s="118" t="s">
+        <v>103</v>
+      </c>
+      <c r="E277" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F277" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G277" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H277" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I277" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J277" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P277" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Q277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X277" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Y277" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z277" s="119" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="115" t="s">
+        <v>395</v>
+      </c>
+      <c r="B278" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C278" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D278" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E278" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F278" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G278" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H278" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I278" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J278" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="K278" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="L278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M278" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="N278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y278" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z278" s="119" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="115" t="s">
+        <v>397</v>
+      </c>
+      <c r="B279" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C279" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D279" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E279" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F279" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G279" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H279" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I279" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="J279" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L279" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="M279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P279" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="Q279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="U279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y279" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z279" s="119" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="115" t="s">
+        <v>399</v>
+      </c>
+      <c r="B280" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C280" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D280" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="E280" s="115" t="s">
+        <v>36</v>
+      </c>
+      <c r="F280" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="G280" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H280" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="I280" s="120">
+        <v>1.0</v>
+      </c>
+      <c r="J280" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="K280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="L280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="M280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="N280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="O280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="P280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Q280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="R280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="S280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="T280" s="118">
+        <v>1.0</v>
+      </c>
+      <c r="U280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="V280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="W280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="X280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Y280" s="118">
+        <v>0.0</v>
+      </c>
+      <c r="Z280" s="122" t="s">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="E120:E139">
